--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J75-TypeAutorisation-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J75-TypeAutorisation-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>Property</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>Agrément de radiophysicien avant le 28/11/2004</t>
+  </si>
+  <si>
+    <t>AM42</t>
+  </si>
+  <si>
+    <t>Autorisation d'user du titre de Psychothérapeute</t>
   </si>
   <si>
     <t/>
@@ -621,7 +627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -961,15 +967,23 @@
         <v>110</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>112</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
